--- a/ID_Colaborador.xlsx
+++ b/ID_Colaborador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inpasabr-my.sharepoint.com/personal/gabriel_oliveira_inpasa_com_br/Documents/Área de Trabalho/CarteirinhaTreinamentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E83D5AB1-FB6B-4FC4-8D1D-FBD66C20978F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{E83D5AB1-FB6B-4FC4-8D1D-FBD66C20978F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9120E67E-138A-4E45-A707-C471BA8FEDCA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{412055B9-DE79-465F-8660-BDEEAC093461}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{412055B9-DE79-465F-8660-BDEEAC093461}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -545,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -559,7 +559,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -573,7 +573,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
